--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:22:23+00:00</t>
+    <t>2025-09-26T14:20:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -356,7 +356,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -633,7 +633,7 @@
     <t>The domestic partnership status of a person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>http://hl7.org/fhir/ValueSet/marital-status|4.0.1</t>
   </si>
   <si>
     <t>Patient.multipleBirth[x]</t>
@@ -757,7 +757,7 @@
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -808,7 +808,7 @@
     <t>Patient.contact.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -899,7 +899,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -958,7 +958,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1327,7 +1327,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="69.35546875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="44.51171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="48.33203125" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.65625" customWidth="true" bestFit="true"/>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-26T14:20:13+00:00</t>
+    <t>2026-06-29T09:18:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:18:12+00:00</t>
+    <t>2026-06-29T11:45:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -120,7 +120,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Patient</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Patient|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
